--- a/results/01_pollution_assessment/SumRel_Focus/tables/SumRel_single_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/SumRel_single_cutoff_metrics.xlsx
@@ -491,25 +491,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01820673095904509</v>
+        <v>0.02266238712790709</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.09088141004550554</v>
+        <v>-0.08593068096899215</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1668992687141456</v>
+        <v>0.2086909185371308</v>
       </c>
       <c r="G2" t="n">
-        <v>0.974</v>
+        <v>0.997</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08617495754290641</v>
+        <v>5.373566099719055</v>
       </c>
       <c r="I2" t="n">
-        <v>4.733137307117441</v>
+        <v>237.113860485681</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00861749575429064</v>
+        <v>0.5373566099719056</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -526,25 +526,25 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008147654813107096</v>
+        <v>0.02285957612896192</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06269894127167097</v>
+        <v>-0.04693616843325499</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1150041817585317</v>
+        <v>0.327521058373187</v>
       </c>
       <c r="G3" t="n">
-        <v>0.998</v>
+        <v>0.969</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06095377574943238</v>
+        <v>8.900554725623618</v>
       </c>
       <c r="I3" t="n">
-        <v>7.481143610965981</v>
+        <v>389.3578199093144</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004063585049962159</v>
+        <v>0.5933703150415747</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -561,25 +561,25 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02350932521148857</v>
+        <v>0.04086404141871653</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03074015672120645</v>
+        <v>-0.01242128961357691</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4333557551877739</v>
+        <v>0.7668910115984998</v>
       </c>
       <c r="G4" t="n">
-        <v>0.823</v>
+        <v>0.597</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2296524999087011</v>
+        <v>21.4430947064078</v>
       </c>
       <c r="I4" t="n">
-        <v>9.768570464815983</v>
+        <v>524.7423887101495</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01208697367940532</v>
+        <v>1.1285839319162</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -596,25 +596,25 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03314731800264124</v>
+        <v>0.04424481593151422</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.008889755127678756</v>
+        <v>0.002690242711145263</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7885258305182332</v>
+        <v>1.064739991357355</v>
       </c>
       <c r="G5" t="n">
-        <v>0.529</v>
+        <v>0.356</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4255294685990728</v>
+        <v>29.99595268391051</v>
       </c>
       <c r="I5" t="n">
-        <v>12.83752334246667</v>
+        <v>677.9540620157787</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01773039452496137</v>
+        <v>1.249831361829605</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -631,25 +631,25 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03898589342804905</v>
+        <v>0.04440301176761348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004663961050479282</v>
+        <v>0.01027454790217108</v>
       </c>
       <c r="F6" t="n">
-        <v>1.135888649833929</v>
+        <v>1.301055094148988</v>
       </c>
       <c r="G6" t="n">
-        <v>0.305</v>
+        <v>0.218</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5949534768322984</v>
+        <v>36.87311040692659</v>
       </c>
       <c r="I6" t="n">
-        <v>15.26073726975946</v>
+        <v>830.419130123533</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02051563713214821</v>
+        <v>1.27148656575609</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -666,25 +666,25 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01954120892821938</v>
+        <v>0.02475110580000515</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01109812829277379</v>
+        <v>-0.005725422143744607</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6377817113756082</v>
+        <v>0.8121366661480591</v>
       </c>
       <c r="G7" t="n">
-        <v>0.652</v>
+        <v>0.552</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3332037339484358</v>
+        <v>23.07260269927427</v>
       </c>
       <c r="I7" t="n">
-        <v>17.05133675057625</v>
+        <v>932.1847228041613</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0100970828469223</v>
+        <v>0.6991697787658869</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -701,25 +701,25 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01472768088408112</v>
+        <v>0.02480737862408462</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01190130071364637</v>
+        <v>-0.00154917871039939</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5530696256644658</v>
+        <v>0.9412222662186357</v>
       </c>
       <c r="G8" t="n">
-        <v>0.678</v>
+        <v>0.422</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2806005152608744</v>
+        <v>26.02600941819714</v>
       </c>
       <c r="I8" t="n">
-        <v>19.05259337633872</v>
+        <v>1049.123722928524</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007384224085812485</v>
+        <v>0.6848949846893981</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -736,25 +736,25 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01472112070662434</v>
+        <v>0.01965172052019707</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.008737900228932061</v>
+        <v>-0.003689905181702979</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6275249400673711</v>
+        <v>0.8419173870394712</v>
       </c>
       <c r="G9" t="n">
-        <v>0.601</v>
+        <v>0.488</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3071650980002898</v>
+        <v>22.78834092789477</v>
       </c>
       <c r="I9" t="n">
-        <v>20.86560555556542</v>
+        <v>1159.610473010444</v>
       </c>
       <c r="J9" t="n">
-        <v>0.007143374372099768</v>
+        <v>0.5299614169277855</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -771,25 +771,25 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01271366134885346</v>
+        <v>0.01377111316215644</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.008749085143562985</v>
+        <v>-0.007668645247361994</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5923594798711236</v>
+        <v>0.6423166203236068</v>
       </c>
       <c r="G10" t="n">
-        <v>0.626</v>
+        <v>0.667</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2833496151574307</v>
+        <v>17.05358368117221</v>
       </c>
       <c r="I10" t="n">
-        <v>22.28701924508817</v>
+        <v>1238.359127571192</v>
       </c>
       <c r="J10" t="n">
-        <v>0.006028715216115548</v>
+        <v>0.3628422059823876</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -806,25 +806,25 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.009362138771797339</v>
+        <v>0.0142563720490988</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01006213301699077</v>
+        <v>-0.005071934381311038</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4819814546252991</v>
+        <v>0.7375903367647775</v>
       </c>
       <c r="G11" t="n">
-        <v>0.747</v>
+        <v>0.597</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2348023213837468</v>
+        <v>20.49322553104173</v>
       </c>
       <c r="I11" t="n">
-        <v>25.07998728784807</v>
+        <v>1437.47830517212</v>
       </c>
       <c r="J11" t="n">
-        <v>0.004515429257379746</v>
+        <v>0.3941004909815715</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -841,25 +841,25 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.005976740848226895</v>
+        <v>0.01075815127548217</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.01177367449376909</v>
+        <v>-0.006906881737455572</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3367099154061169</v>
+        <v>0.609008274572877</v>
       </c>
       <c r="G12" t="n">
-        <v>0.866</v>
+        <v>0.698</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1617589890037821</v>
+        <v>16.55471743826506</v>
       </c>
       <c r="I12" t="n">
-        <v>27.06474868351884</v>
+        <v>1538.806902259616</v>
       </c>
       <c r="J12" t="n">
-        <v>0.002837877000066354</v>
+        <v>0.2904336392678081</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -876,25 +876,25 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003523441119839894</v>
+        <v>0.006998448733289412</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01308450152816265</v>
+        <v>-0.009551577121155841</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2121539792446017</v>
+        <v>0.4228663323453176</v>
       </c>
       <c r="G13" t="n">
-        <v>0.95</v>
+        <v>0.875</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1004763638003682</v>
+        <v>11.37952757825793</v>
       </c>
       <c r="I13" t="n">
-        <v>28.51654402129866</v>
+        <v>1626.007135571217</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001647153504924067</v>
+        <v>0.1865496324304579</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -911,25 +911,25 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002893576774599962</v>
+        <v>0.007827426813231095</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01244652204425223</v>
+        <v>-0.007436766620411372</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1886283008192804</v>
+        <v>0.5127966208800318</v>
       </c>
       <c r="G14" t="n">
-        <v>0.967</v>
+        <v>0.826</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0932944551112493</v>
+        <v>14.63296832982321</v>
       </c>
       <c r="I14" t="n">
-        <v>32.24191455025323</v>
+        <v>1869.448118644606</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001413552350170445</v>
+        <v>0.2217116413609579</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -946,25 +946,25 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.003382217951642824</v>
+        <v>0.007077908636783209</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01085517893476218</v>
+        <v>-0.007106692668405579</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2375587320230154</v>
+        <v>0.4989853774877739</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.822</v>
       </c>
       <c r="H15" t="n">
-        <v>0.117596622929324</v>
+        <v>14.20308820048408</v>
       </c>
       <c r="I15" t="n">
-        <v>34.7690848462928</v>
+        <v>2006.678657403402</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001656290463793296</v>
+        <v>0.2000434957814658</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -981,25 +981,25 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002033533805238301</v>
+        <v>0.00819753476775615</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01145249952171801</v>
+        <v>-0.005205201248895897</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1507881343562765</v>
+        <v>0.6116314428316201</v>
       </c>
       <c r="G16" t="n">
-        <v>0.985</v>
+        <v>0.7</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07352259513542084</v>
+        <v>17.22415879670475</v>
       </c>
       <c r="I16" t="n">
-        <v>36.15508871602214</v>
+        <v>2101.138852677216</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0009803012684722781</v>
+        <v>0.2296554506227301</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1016,25 +1016,25 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001310524433623104</v>
+        <v>0.006429651664818219</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01133111449759694</v>
+        <v>-0.006147188187525909</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1036672887711272</v>
+        <v>0.5112295091854779</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05083219815020602</v>
+        <v>14.40861561234525</v>
       </c>
       <c r="I17" t="n">
-        <v>38.78767678499075</v>
+        <v>2240.963642118645</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0006354024768775751</v>
+        <v>0.1801076951543156</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1051,25 +1051,25 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.002894979719508601</v>
+        <v>0.007933392904458509</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.008975318140973521</v>
+        <v>-0.003876923846678926</v>
       </c>
       <c r="F18" t="n">
-        <v>0.243884336647222</v>
+        <v>0.6717341347931653</v>
       </c>
       <c r="G18" t="n">
-        <v>0.961</v>
+        <v>0.645</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1211146302089039</v>
+        <v>19.36005200538812</v>
       </c>
       <c r="I18" t="n">
-        <v>41.83608934899969</v>
+        <v>2440.324365443682</v>
       </c>
       <c r="J18" t="n">
-        <v>0.001424878002457694</v>
+        <v>0.2277653177104484</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1086,25 +1086,25 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.005551511928657244</v>
+        <v>0.00585922913335602</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.005749039072153517</v>
+        <v>-0.00543782508103785</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4912602870655576</v>
+        <v>0.5186510591310363</v>
       </c>
       <c r="G19" t="n">
-        <v>0.739</v>
+        <v>0.803</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2428408264542581</v>
+        <v>14.7036955726183</v>
       </c>
       <c r="I19" t="n">
-        <v>43.74318736499491</v>
+        <v>2509.493183823722</v>
       </c>
       <c r="J19" t="n">
-        <v>0.002728548611845597</v>
+        <v>0.1652100626136889</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1121,25 +1121,25 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.008490429387400066</v>
+        <v>0.005781072814483268</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.002170963844993379</v>
+        <v>-0.004909453284285714</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7963714687497659</v>
+        <v>0.5407659792485753</v>
       </c>
       <c r="G20" t="n">
-        <v>0.526</v>
+        <v>0.803</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3904538291291174</v>
+        <v>15.24653596091313</v>
       </c>
       <c r="I20" t="n">
-        <v>45.98752446001815</v>
+        <v>2637.31948207193</v>
       </c>
       <c r="J20" t="n">
-        <v>0.004153764139671464</v>
+        <v>0.1621971910735439</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1156,25 +1156,25 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01204992981860516</v>
+        <v>0.005083311992367624</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001968806653488975</v>
+        <v>-0.005068899109750946</v>
       </c>
       <c r="F21" t="n">
-        <v>1.195296359467321</v>
+        <v>0.5007098395842823</v>
       </c>
       <c r="G21" t="n">
-        <v>0.304</v>
+        <v>0.848</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5781182391959296</v>
+        <v>14.03026124453807</v>
       </c>
       <c r="I21" t="n">
-        <v>47.97689678684369</v>
+        <v>2760.062979727373</v>
       </c>
       <c r="J21" t="n">
-        <v>0.005839578173696261</v>
+        <v>0.1417198105508896</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1191,25 +1191,25 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01089784898678452</v>
+        <v>0.00479901309827974</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001200769074890196</v>
+        <v>-0.004957859322325175</v>
       </c>
       <c r="F22" t="n">
-        <v>1.123827903430743</v>
+        <v>0.4918597775394623</v>
       </c>
       <c r="G22" t="n">
-        <v>0.304</v>
+        <v>0.847</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5492280778671368</v>
+        <v>13.78022798467055</v>
       </c>
       <c r="I22" t="n">
-        <v>50.39784259565064</v>
+        <v>2871.471217615602</v>
       </c>
       <c r="J22" t="n">
-        <v>0.005332311435603271</v>
+        <v>0.1337886212103936</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1226,25 +1226,25 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01140521716500348</v>
+        <v>0.003613590009249645</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00216601358710633</v>
+        <v>-0.005698432514028351</v>
       </c>
       <c r="F23" t="n">
-        <v>1.234437261701652</v>
+        <v>0.3880564077477747</v>
       </c>
       <c r="G23" t="n">
-        <v>0.268</v>
+        <v>0.929</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5906493217072758</v>
+        <v>10.66091797769133</v>
       </c>
       <c r="I23" t="n">
-        <v>51.78764359872631</v>
+        <v>2950.228982923563</v>
       </c>
       <c r="J23" t="n">
-        <v>0.005468975200993293</v>
+        <v>0.09871220349714191</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -1261,25 +1261,25 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01699566332582121</v>
+        <v>0.007180532392186778</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008218838891230429</v>
+        <v>-0.001683927140025743</v>
       </c>
       <c r="F24" t="n">
-        <v>1.936425121919786</v>
+        <v>0.8100361185127409</v>
       </c>
       <c r="G24" t="n">
-        <v>0.115</v>
+        <v>0.489</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9318791877649537</v>
+        <v>22.49366803776725</v>
       </c>
       <c r="I24" t="n">
-        <v>54.83040996400337</v>
+        <v>3132.590566995127</v>
       </c>
       <c r="J24" t="n">
-        <v>0.008246718475796045</v>
+        <v>0.1990590091837811</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1296,25 +1296,25 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01130106530350011</v>
+        <v>0.005783585518961077</v>
       </c>
       <c r="E25" t="n">
-        <v>0.002777798625081984</v>
+        <v>-0.002787245640358149</v>
       </c>
       <c r="F25" t="n">
-        <v>1.325907745221174</v>
+        <v>0.6747986760505049</v>
       </c>
       <c r="G25" t="n">
-        <v>0.246</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6433370644602925</v>
+        <v>18.79497719120003</v>
       </c>
       <c r="I25" t="n">
-        <v>56.92711679677149</v>
+        <v>3249.710258382456</v>
       </c>
       <c r="J25" t="n">
-        <v>0.005498607388549504</v>
+        <v>0.1606408306940175</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -1331,25 +1331,25 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01509303587655802</v>
+        <v>0.008466771903940537</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00695330890033119</v>
+        <v>0.0002722824155433345</v>
       </c>
       <c r="F26" t="n">
-        <v>1.854243504805424</v>
+        <v>1.033227501960785</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11</v>
+        <v>0.384</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8985201657879629</v>
+        <v>28.42641715680328</v>
       </c>
       <c r="I26" t="n">
-        <v>59.53210296038012</v>
+        <v>3357.409114041832</v>
       </c>
       <c r="J26" t="n">
-        <v>0.007364919391704613</v>
+        <v>0.2330034193180595</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1366,25 +1366,25 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01447482241768095</v>
+        <v>0.008818389808069141</v>
       </c>
       <c r="E27" t="n">
-        <v>0.006653194024170528</v>
+        <v>0.0009518690922601936</v>
       </c>
       <c r="F27" t="n">
-        <v>1.850614947354259</v>
+        <v>1.121002553307619</v>
       </c>
       <c r="G27" t="n">
-        <v>0.124</v>
+        <v>0.309</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8921813752047656</v>
+        <v>30.55693763389969</v>
       </c>
       <c r="I27" t="n">
-        <v>61.63677518523258</v>
+        <v>3465.138001264018</v>
       </c>
       <c r="J27" t="n">
-        <v>0.007025050198462723</v>
+        <v>0.2406058081409424</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -1401,25 +1401,25 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.009478986411808072</v>
+        <v>0.00729356185579655</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001859593999591236</v>
+        <v>-0.0003426415145435513</v>
       </c>
       <c r="F28" t="n">
-        <v>1.244060667699639</v>
+        <v>0.9551293361470258</v>
       </c>
       <c r="G28" t="n">
-        <v>0.253</v>
+        <v>0.406</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5980419044423686</v>
+        <v>25.83292848979556</v>
       </c>
       <c r="I28" t="n">
-        <v>63.09133471247323</v>
+        <v>3541.881045303655</v>
       </c>
       <c r="J28" t="n">
-        <v>0.004565205377422661</v>
+        <v>0.1971979274030195</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1436,25 +1436,25 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0139682654448677</v>
+        <v>0.00918744567847766</v>
       </c>
       <c r="E29" t="n">
-        <v>0.006664326670385412</v>
+        <v>0.00184809342424419</v>
       </c>
       <c r="F29" t="n">
-        <v>1.912429153112317</v>
+        <v>1.251806066833506</v>
       </c>
       <c r="G29" t="n">
-        <v>0.098</v>
+        <v>0.224</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9110920136844529</v>
+        <v>33.82286466517058</v>
       </c>
       <c r="I29" t="n">
-        <v>65.22585193419354</v>
+        <v>3681.422002244149</v>
       </c>
       <c r="J29" t="n">
-        <v>0.006699205982973914</v>
+        <v>0.248697534302725</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -1471,25 +1471,25 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01226884024694275</v>
+        <v>0.009932071789190412</v>
       </c>
       <c r="E30" t="n">
-        <v>0.005213617677278126</v>
+        <v>0.002860158016256054</v>
       </c>
       <c r="F30" t="n">
-        <v>1.738972814223469</v>
+        <v>1.40443903985403</v>
       </c>
       <c r="G30" t="n">
-        <v>0.122</v>
+        <v>0.158</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8185444861456033</v>
+        <v>37.27585600441313</v>
       </c>
       <c r="I30" t="n">
-        <v>66.7173481494777</v>
+        <v>3753.07959865759</v>
       </c>
       <c r="J30" t="n">
-        <v>0.005805280043585839</v>
+        <v>0.2643677730809443</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1506,25 +1506,25 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01253611599262496</v>
+        <v>0.009516461039454444</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0056787279092404</v>
+        <v>0.002638103130006231</v>
       </c>
       <c r="F31" t="n">
-        <v>1.828118204801617</v>
+        <v>1.383536763386864</v>
       </c>
       <c r="G31" t="n">
-        <v>0.124</v>
+        <v>0.183</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8529589594216604</v>
+        <v>36.42741490066355</v>
       </c>
       <c r="I31" t="n">
-        <v>68.04012980762613</v>
+        <v>3827.832084809528</v>
       </c>
       <c r="J31" t="n">
-        <v>0.005882475582218344</v>
+        <v>0.251223551039059</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1541,25 +1541,25 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01381480609746646</v>
+        <v>0.009459882503292273</v>
       </c>
       <c r="E32" t="n">
-        <v>0.007196113520939296</v>
+        <v>0.002811962251636491</v>
       </c>
       <c r="F32" t="n">
-        <v>2.087240937350696</v>
+        <v>1.422983752089408</v>
       </c>
       <c r="G32" t="n">
-        <v>0.077</v>
+        <v>0.172</v>
       </c>
       <c r="H32" t="n">
-        <v>0.975452477709407</v>
+        <v>37.42776774691912</v>
       </c>
       <c r="I32" t="n">
-        <v>70.60920514029499</v>
+        <v>3956.472792753328</v>
       </c>
       <c r="J32" t="n">
-        <v>0.006503016518062713</v>
+        <v>0.2495184516461276</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -1576,25 +1576,25 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01427511621518163</v>
+        <v>0.009722471075695134</v>
       </c>
       <c r="E33" t="n">
-        <v>0.007874305281513894</v>
+        <v>0.003292097511251479</v>
       </c>
       <c r="F33" t="n">
-        <v>2.230204323032866</v>
+        <v>1.511960538257855</v>
       </c>
       <c r="G33" t="n">
-        <v>0.054</v>
+        <v>0.141</v>
       </c>
       <c r="H33" t="n">
-        <v>1.045425060724292</v>
+        <v>40.08424505831165</v>
       </c>
       <c r="I33" t="n">
-        <v>73.23408404987129</v>
+        <v>4122.845390460133</v>
       </c>
       <c r="J33" t="n">
-        <v>0.006744677811124465</v>
+        <v>0.2586080326342688</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -1611,25 +1611,25 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01354442559839149</v>
+        <v>0.009161515358119633</v>
       </c>
       <c r="E34" t="n">
-        <v>0.007301035886988938</v>
+        <v>0.002890385708487431</v>
       </c>
       <c r="F34" t="n">
-        <v>2.169402556059362</v>
+        <v>1.460903516586843</v>
       </c>
       <c r="G34" t="n">
-        <v>0.061</v>
+        <v>0.148</v>
       </c>
       <c r="H34" t="n">
-        <v>1.023503990815404</v>
+        <v>39.15574050879979</v>
       </c>
       <c r="I34" t="n">
-        <v>75.56643752666432</v>
+        <v>4273.937113918277</v>
       </c>
       <c r="J34" t="n">
-        <v>0.00643713201770694</v>
+        <v>0.2462625189232691</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -1646,25 +1646,25 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.008553422568660391</v>
+        <v>0.006618537379638296</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002470928228590852</v>
+        <v>0.0005241725782864082</v>
       </c>
       <c r="F35" t="n">
-        <v>1.406236009512269</v>
+        <v>1.086009386600898</v>
       </c>
       <c r="G35" t="n">
-        <v>0.214</v>
+        <v>0.302</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6740967263794427</v>
+        <v>29.41734211713435</v>
       </c>
       <c r="I35" t="n">
-        <v>78.8101746369135</v>
+        <v>4444.689276460959</v>
       </c>
       <c r="J35" t="n">
-        <v>0.00411034589255758</v>
+        <v>0.1793740372995998</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1681,25 +1681,25 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.008658474579839294</v>
+        <v>0.007281561955579515</v>
       </c>
       <c r="E36" t="n">
-        <v>0.002757632166624058</v>
+        <v>0.001372523633886513</v>
       </c>
       <c r="F36" t="n">
-        <v>1.467328556419028</v>
+        <v>1.23227529746216</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2</v>
+        <v>0.254</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6984978733024401</v>
+        <v>33.27931532695398</v>
       </c>
       <c r="I36" t="n">
-        <v>80.67216307695213</v>
+        <v>4570.35393367128</v>
       </c>
       <c r="J36" t="n">
-        <v>0.004133123510665328</v>
+        <v>0.196919025603278</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1716,25 +1716,25 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.007819815423545703</v>
+        <v>0.006022341323910664</v>
       </c>
       <c r="E37" t="n">
-        <v>0.002051325978333796</v>
+        <v>0.0002434014478869262</v>
       </c>
       <c r="F37" t="n">
-        <v>1.355608863952492</v>
+        <v>1.04211870223754</v>
       </c>
       <c r="G37" t="n">
-        <v>0.238</v>
+        <v>0.361</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6483188234328734</v>
+        <v>28.46697078450602</v>
       </c>
       <c r="I37" t="n">
-        <v>82.90717725648173</v>
+        <v>4726.894284700011</v>
       </c>
       <c r="J37" t="n">
-        <v>0.003747507649901002</v>
+        <v>0.1645489640722892</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1751,25 +1751,25 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.008058922668759131</v>
+        <v>0.006701025033198496</v>
       </c>
       <c r="E38" t="n">
-        <v>0.002454735791181495</v>
+        <v>0.001089166417566734</v>
       </c>
       <c r="F38" t="n">
-        <v>1.438018189757894</v>
+        <v>1.194083011024728</v>
       </c>
       <c r="G38" t="n">
-        <v>0.202</v>
+        <v>0.283</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6880737649385333</v>
+        <v>32.7478460332174</v>
       </c>
       <c r="I38" t="n">
-        <v>85.38036574117905</v>
+        <v>4886.990553083545</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003865582949092883</v>
+        <v>0.1839766631079629</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1786,25 +1786,25 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.009869805429785874</v>
+        <v>0.00811350863539115</v>
       </c>
       <c r="E39" t="n">
-        <v>0.004429529635444074</v>
+        <v>0.002663582858662528</v>
       </c>
       <c r="F39" t="n">
-        <v>1.814210492793578</v>
+        <v>1.488737455845018</v>
       </c>
       <c r="G39" t="n">
-        <v>0.118</v>
+        <v>0.161</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8579716168524383</v>
+        <v>40.62855775638363</v>
       </c>
       <c r="I39" t="n">
-        <v>86.92892914212717</v>
+        <v>5007.520122572094</v>
       </c>
       <c r="J39" t="n">
-        <v>0.004688369490996932</v>
+        <v>0.2220139768108395</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -1821,25 +1821,25 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.01079591684756868</v>
+        <v>0.008449010294435485</v>
       </c>
       <c r="E40" t="n">
-        <v>0.005477615325243712</v>
+        <v>0.003118090994943201</v>
       </c>
       <c r="F40" t="n">
-        <v>2.02995576731596</v>
+        <v>1.584906808707491</v>
       </c>
       <c r="G40" t="n">
-        <v>0.089</v>
+        <v>0.148</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9550789910728764</v>
+        <v>43.20937952879291</v>
       </c>
       <c r="I40" t="n">
-        <v>88.46668648508228</v>
+        <v>5114.135031561104</v>
       </c>
       <c r="J40" t="n">
-        <v>0.00510737428381217</v>
+        <v>0.2310662006887322</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -1856,25 +1856,25 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.007063126698917958</v>
+        <v>0.007329538588903467</v>
       </c>
       <c r="E41" t="n">
-        <v>0.001864504325613914</v>
+        <v>0.002132311042248647</v>
       </c>
       <c r="F41" t="n">
-        <v>1.358653541597567</v>
+        <v>1.410278561619053</v>
       </c>
       <c r="G41" t="n">
-        <v>0.266</v>
+        <v>0.196</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6397855874781607</v>
+        <v>38.66472845696204</v>
       </c>
       <c r="I41" t="n">
-        <v>90.58107191764991</v>
+        <v>5275.192699783092</v>
       </c>
       <c r="J41" t="n">
-        <v>0.003332216601448753</v>
+        <v>0.2013787940466772</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -1891,25 +1891,25 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.007591322900608743</v>
+        <v>0.007152079722855433</v>
       </c>
       <c r="E42" t="n">
-        <v>0.002528013323570999</v>
+        <v>0.0020865291091966</v>
       </c>
       <c r="F42" t="n">
-        <v>1.499280813291698</v>
+        <v>1.411905687719387</v>
       </c>
       <c r="G42" t="n">
-        <v>0.186</v>
+        <v>0.18</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7003464046891323</v>
+        <v>38.42622572844039</v>
       </c>
       <c r="I42" t="n">
-        <v>92.25617377347656</v>
+        <v>5372.734535612657</v>
       </c>
       <c r="J42" t="n">
-        <v>0.003555057891823009</v>
+        <v>0.1950569833930983</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -1926,25 +1926,25 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.009488929315369531</v>
+        <v>0.007981493875672022</v>
       </c>
       <c r="E43" t="n">
-        <v>0.004536373961946394</v>
+        <v>0.003021401345050467</v>
       </c>
       <c r="F43" t="n">
-        <v>1.9159663321705</v>
+        <v>1.609142133215752</v>
       </c>
       <c r="G43" t="n">
-        <v>0.118</v>
+        <v>0.124</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8935450545798096</v>
+        <v>43.67341292795399</v>
       </c>
       <c r="I43" t="n">
-        <v>94.16711041703148</v>
+        <v>5471.834422008724</v>
       </c>
       <c r="J43" t="n">
-        <v>0.004445497783979154</v>
+        <v>0.2172806613331044</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
@@ -1961,25 +1961,25 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01123445034605362</v>
+        <v>0.008527756639643917</v>
       </c>
       <c r="E44" t="n">
-        <v>0.006411203762375806</v>
+        <v>0.003691306672032435</v>
       </c>
       <c r="F44" t="n">
-        <v>2.32922993903563</v>
+        <v>1.763226477427077</v>
       </c>
       <c r="G44" t="n">
-        <v>0.053</v>
+        <v>0.096</v>
       </c>
       <c r="H44" t="n">
-        <v>1.079799642038332</v>
+        <v>47.64192668294518</v>
       </c>
       <c r="I44" t="n">
-        <v>96.1150397907663</v>
+        <v>5586.689289591935</v>
       </c>
       <c r="J44" t="n">
-        <v>0.005241745835137535</v>
+        <v>0.2312714887521613</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -1996,25 +1996,25 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01067953806304918</v>
+        <v>0.008111891581495939</v>
       </c>
       <c r="E45" t="n">
-        <v>0.005968488244301851</v>
+        <v>0.00338861487474118</v>
       </c>
       <c r="F45" t="n">
-        <v>2.266912572342262</v>
+        <v>1.717428828570447</v>
       </c>
       <c r="G45" t="n">
-        <v>0.075</v>
+        <v>0.121</v>
       </c>
       <c r="H45" t="n">
-        <v>1.051199269403623</v>
+        <v>45.98818162914067</v>
       </c>
       <c r="I45" t="n">
-        <v>98.43115528008981</v>
+        <v>5669.230310479549</v>
       </c>
       <c r="J45" t="n">
-        <v>0.004981987058784946</v>
+        <v>0.2179534674366856</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -2031,25 +2031,25 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01151720925553366</v>
+        <v>0.007766551488017704</v>
       </c>
       <c r="E46" t="n">
-        <v>0.006898130794110835</v>
+        <v>0.003129946588429022</v>
       </c>
       <c r="F46" t="n">
-        <v>2.493399787797975</v>
+        <v>1.675051391311485</v>
       </c>
       <c r="G46" t="n">
-        <v>0.051</v>
+        <v>0.106</v>
       </c>
       <c r="H46" t="n">
-        <v>1.15481751804954</v>
+        <v>44.79488593322327</v>
       </c>
       <c r="I46" t="n">
-        <v>100.2688665654561</v>
+        <v>5767.667413566132</v>
       </c>
       <c r="J46" t="n">
-        <v>0.005371244269997859</v>
+        <v>0.2083483066661547</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -2066,25 +2066,25 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01381218628303095</v>
+        <v>0.009289322132112159</v>
       </c>
       <c r="E47" t="n">
-        <v>0.009309045581126996</v>
+        <v>0.004765529082487174</v>
       </c>
       <c r="F47" t="n">
-        <v>3.06723400341256</v>
+        <v>2.053436580809565</v>
       </c>
       <c r="G47" t="n">
-        <v>0.031</v>
+        <v>0.068</v>
       </c>
       <c r="H47" t="n">
-        <v>1.405677394505826</v>
+        <v>54.48540707547501</v>
       </c>
       <c r="I47" t="n">
-        <v>101.7708106234261</v>
+        <v>5865.380304459997</v>
       </c>
       <c r="J47" t="n">
-        <v>0.006389442702299209</v>
+        <v>0.2476609412521591</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -2101,25 +2101,25 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01748601732470403</v>
+        <v>0.01037797495634475</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01309979418776064</v>
+        <v>0.00596001948739977</v>
       </c>
       <c r="F48" t="n">
-        <v>3.986577239408266</v>
+        <v>2.349044717470465</v>
       </c>
       <c r="G48" t="n">
-        <v>0.006</v>
+        <v>0.039</v>
       </c>
       <c r="H48" t="n">
-        <v>1.805417984487521</v>
+        <v>61.72923771638558</v>
       </c>
       <c r="I48" t="n">
-        <v>103.2492391470326</v>
+        <v>5948.100470087027</v>
       </c>
       <c r="J48" t="n">
-        <v>0.008024079931055646</v>
+        <v>0.2743521676283804</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -2136,25 +2136,25 @@
         <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.01630103077351188</v>
+        <v>0.0100692791705544</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01198656161023792</v>
+        <v>0.005727477763407873</v>
       </c>
       <c r="F49" t="n">
-        <v>3.778223961425119</v>
+        <v>2.319147797497178</v>
       </c>
       <c r="G49" t="n">
-        <v>0.008</v>
+        <v>0.037</v>
       </c>
       <c r="H49" t="n">
-        <v>1.711582564160943</v>
+        <v>60.99952929470849</v>
       </c>
       <c r="I49" t="n">
-        <v>104.9984254334489</v>
+        <v>6057.983720730425</v>
       </c>
       <c r="J49" t="n">
-        <v>0.007474159668825076</v>
+        <v>0.266373490369906</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>

--- a/results/01_pollution_assessment/SumRel_Focus/tables/SumRel_single_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/SumRel_single_cutoff_metrics.xlsx
@@ -488,28 +488,28 @@
         <v>0.05</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02266238712790709</v>
+        <v>0.1343547582722011</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.08593068096899215</v>
+        <v>0.06776666275467813</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2086909185371308</v>
+        <v>2.017699368453104</v>
       </c>
       <c r="G2" t="n">
-        <v>0.997</v>
+        <v>0.095</v>
       </c>
       <c r="H2" t="n">
-        <v>5.373566099719055</v>
+        <v>41.79168011798258</v>
       </c>
       <c r="I2" t="n">
-        <v>237.113860485681</v>
+        <v>311.0547081132261</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5373566099719056</v>
+        <v>2.985120008427327</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -523,28 +523,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02285957612896192</v>
+        <v>0.0481288230804835</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.04693616843325499</v>
+        <v>-0.001969659915280531</v>
       </c>
       <c r="F3" t="n">
-        <v>0.327521058373187</v>
+        <v>0.9606842403701712</v>
       </c>
       <c r="G3" t="n">
-        <v>0.969</v>
+        <v>0.438</v>
       </c>
       <c r="H3" t="n">
-        <v>8.900554725623618</v>
+        <v>20.25237696540423</v>
       </c>
       <c r="I3" t="n">
-        <v>389.3578199093144</v>
+        <v>420.7951840321789</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5933703150415747</v>
+        <v>1.012618848270211</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -558,28 +558,28 @@
         <v>0.09</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04086404141871653</v>
+        <v>0.06840106269008149</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01242128961357691</v>
+        <v>0.03113710519768476</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7668910115984998</v>
+        <v>1.835582350694714</v>
       </c>
       <c r="G4" t="n">
-        <v>0.597</v>
+        <v>0.11</v>
       </c>
       <c r="H4" t="n">
-        <v>21.4430947064078</v>
+        <v>39.74632712226193</v>
       </c>
       <c r="I4" t="n">
-        <v>524.7423887101495</v>
+        <v>581.0776259770794</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1285839319162</v>
+        <v>1.528704889317767</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -593,28 +593,28 @@
         <v>0.11</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04424481593151422</v>
+        <v>0.05504500847979561</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002690242711145263</v>
+        <v>0.02551516499478923</v>
       </c>
       <c r="F5" t="n">
-        <v>1.064739991357355</v>
+        <v>1.864046739961368</v>
       </c>
       <c r="G5" t="n">
-        <v>0.356</v>
+        <v>0.108</v>
       </c>
       <c r="H5" t="n">
-        <v>29.99595268391051</v>
+        <v>38.6651998044837</v>
       </c>
       <c r="I5" t="n">
-        <v>677.9540620157787</v>
+        <v>702.4288100287212</v>
       </c>
       <c r="J5" t="n">
-        <v>1.249831361829605</v>
+        <v>1.171672721347991</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -628,28 +628,28 @@
         <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04440301176761348</v>
+        <v>0.05389415588297435</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01027454790217108</v>
+        <v>0.02899663366936833</v>
       </c>
       <c r="F6" t="n">
-        <v>1.301055094148988</v>
+        <v>2.164639333207317</v>
       </c>
       <c r="G6" t="n">
-        <v>0.218</v>
+        <v>0.057</v>
       </c>
       <c r="H6" t="n">
-        <v>36.87311040692659</v>
+        <v>42.62214316319016</v>
       </c>
       <c r="I6" t="n">
-        <v>830.419130123533</v>
+        <v>790.8490719427871</v>
       </c>
       <c r="J6" t="n">
-        <v>1.27148656575609</v>
+        <v>1.092875465722825</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -663,28 +663,28 @@
         <v>0.15</v>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02475110580000515</v>
+        <v>0.04401686981157218</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.005725422143744607</v>
+        <v>0.02228998048910791</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8121366661480591</v>
+        <v>2.025916787179536</v>
       </c>
       <c r="G7" t="n">
-        <v>0.552</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>23.07260269927427</v>
+        <v>41.25617865491397</v>
       </c>
       <c r="I7" t="n">
-        <v>932.1847228041613</v>
+        <v>937.2810659077712</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6991697787658869</v>
+        <v>0.9168039701091987</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -698,28 +698,28 @@
         <v>0.17</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02480737862408462</v>
+        <v>0.03304315799902453</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.00154917871039939</v>
+        <v>0.01370402115900504</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9412222662186357</v>
+        <v>1.708615967319004</v>
       </c>
       <c r="G8" t="n">
-        <v>0.422</v>
+        <v>0.125</v>
       </c>
       <c r="H8" t="n">
-        <v>26.02600941819714</v>
+        <v>38.31202882667672</v>
       </c>
       <c r="I8" t="n">
-        <v>1049.123722928524</v>
+        <v>1159.454215235957</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6848949846893981</v>
+        <v>0.7512162515034653</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -733,28 +733,28 @@
         <v>0.19</v>
       </c>
       <c r="C9" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01965172052019707</v>
+        <v>0.0313986395467045</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.003689905181702979</v>
+        <v>0.01410218668146712</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8419173870394712</v>
+        <v>1.815322470528613</v>
       </c>
       <c r="G9" t="n">
-        <v>0.488</v>
+        <v>0.095</v>
       </c>
       <c r="H9" t="n">
-        <v>22.78834092789477</v>
+        <v>40.86784678954074</v>
       </c>
       <c r="I9" t="n">
-        <v>1159.610473010444</v>
+        <v>1301.580176069447</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5299614169277855</v>
+        <v>0.7169797682375573</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -768,28 +768,28 @@
         <v>0.21</v>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01377111316215644</v>
+        <v>0.02830411144828157</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.007668645247361994</v>
+        <v>0.01288036718555596</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6423166203236068</v>
+        <v>1.835099893135783</v>
       </c>
       <c r="G10" t="n">
-        <v>0.667</v>
+        <v>0.092</v>
       </c>
       <c r="H10" t="n">
-        <v>17.05358368117221</v>
+        <v>43.34061093145996</v>
       </c>
       <c r="I10" t="n">
-        <v>1238.359127571192</v>
+        <v>1531.247889927713</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3628422059823876</v>
+        <v>0.6771970458040619</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -803,28 +803,28 @@
         <v>0.23</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0142563720490988</v>
+        <v>0.02918701822684298</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.005071934381311038</v>
+        <v>0.01511726486781162</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7375903367647775</v>
+        <v>2.074451305723001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.597</v>
+        <v>0.049</v>
       </c>
       <c r="H11" t="n">
-        <v>20.49322553104173</v>
+        <v>47.77410718496151</v>
       </c>
       <c r="I11" t="n">
-        <v>1437.47830517212</v>
+        <v>1636.827263876657</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3941004909815715</v>
+        <v>0.6824872454994503</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -838,28 +838,28 @@
         <v>0.25</v>
       </c>
       <c r="C12" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01075815127548217</v>
+        <v>0.0387055046905635</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.006906881737455572</v>
+        <v>0.02588824475310436</v>
       </c>
       <c r="F12" t="n">
-        <v>0.609008274572877</v>
+        <v>3.019795563125353</v>
       </c>
       <c r="G12" t="n">
-        <v>0.698</v>
+        <v>0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>16.55471743826506</v>
+        <v>68.74811577124862</v>
       </c>
       <c r="I12" t="n">
-        <v>1538.806902259616</v>
+        <v>1776.184455437668</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2904336392678081</v>
+        <v>0.9045804706743241</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -873,28 +873,28 @@
         <v>0.27</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.006998448733289412</v>
+        <v>0.03641551275115183</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.009551577121155841</v>
+        <v>0.02451940797030183</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4228663323453176</v>
+        <v>3.061129119320849</v>
       </c>
       <c r="G13" t="n">
-        <v>0.875</v>
+        <v>0.011</v>
       </c>
       <c r="H13" t="n">
-        <v>11.37952757825793</v>
+        <v>71.54382009164084</v>
       </c>
       <c r="I13" t="n">
-        <v>1626.007135571217</v>
+        <v>1964.652278289776</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1865496324304579</v>
+        <v>0.8724856108736692</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -908,28 +908,28 @@
         <v>0.29</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.007827426813231095</v>
+        <v>0.03359390921283926</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.007436766620411372</v>
+        <v>0.02248579322677979</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5127966208800318</v>
+        <v>3.024267054377142</v>
       </c>
       <c r="G14" t="n">
-        <v>0.826</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>14.63296832982321</v>
+        <v>71.65637540578577</v>
       </c>
       <c r="I14" t="n">
-        <v>1869.448118644606</v>
+        <v>2133.016879690781</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2217116413609579</v>
+        <v>0.8142769932475656</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -943,28 +943,28 @@
         <v>0.31</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.007077908636783209</v>
+        <v>0.03821215594670818</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.007106692668405579</v>
+        <v>0.027980370371673</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4989853774877739</v>
+        <v>3.734651754229847</v>
       </c>
       <c r="G15" t="n">
-        <v>0.822</v>
+        <v>0.003</v>
       </c>
       <c r="H15" t="n">
-        <v>14.20308820048408</v>
+        <v>86.89963145042185</v>
       </c>
       <c r="I15" t="n">
-        <v>2006.678657403402</v>
+        <v>2274.135789972559</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2000434957814658</v>
+        <v>0.9147329626360193</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -978,28 +978,28 @@
         <v>0.33</v>
       </c>
       <c r="C16" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00819753476775615</v>
+        <v>0.04330395020545587</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.005205201248895897</v>
+        <v>0.03373698970751038</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6116314428316201</v>
+        <v>4.52640629327942</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7</v>
+        <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>17.22415879670475</v>
+        <v>105.7681619497189</v>
       </c>
       <c r="I16" t="n">
-        <v>2101.138852677216</v>
+        <v>2442.459901415486</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2296554506227301</v>
+        <v>1.047209524254643</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1013,28 +1013,28 @@
         <v>0.35</v>
       </c>
       <c r="C17" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.006429651664818219</v>
+        <v>0.04507400869751438</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.006147188187525909</v>
+        <v>0.03606527293050965</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5112295091854779</v>
+        <v>5.003366716848611</v>
       </c>
       <c r="G17" t="n">
-        <v>0.84</v>
+        <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>14.40861561234525</v>
+        <v>114.3700791458616</v>
       </c>
       <c r="I17" t="n">
-        <v>2240.963642118645</v>
+        <v>2537.384236520515</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1801076951543156</v>
+        <v>1.068879244353846</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1048,28 +1048,28 @@
         <v>0.37</v>
       </c>
       <c r="C18" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.007933392904458509</v>
+        <v>0.03488805987272605</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.003876923846678926</v>
+        <v>0.02627098897873259</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6717341347931653</v>
+        <v>4.048714499615477</v>
       </c>
       <c r="G18" t="n">
-        <v>0.645</v>
+        <v>0.002</v>
       </c>
       <c r="H18" t="n">
-        <v>19.36005200538812</v>
+        <v>100.5126740482152</v>
       </c>
       <c r="I18" t="n">
-        <v>2440.324365443682</v>
+        <v>2881.004974621463</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2277653177104484</v>
+        <v>0.8894926906921699</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1083,28 +1083,28 @@
         <v>0.39</v>
       </c>
       <c r="C19" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00585922913335602</v>
+        <v>0.03392185882007112</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.00543782508103785</v>
+        <v>0.02573475592871588</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5186510591310363</v>
+        <v>4.143328753799935</v>
       </c>
       <c r="G19" t="n">
-        <v>0.803</v>
+        <v>0.006</v>
       </c>
       <c r="H19" t="n">
-        <v>14.7036955726183</v>
+        <v>104.4307817734263</v>
       </c>
       <c r="I19" t="n">
-        <v>2509.493183823722</v>
+        <v>3078.568964258409</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1652100626136889</v>
+        <v>0.8775695947346751</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1118,28 +1118,28 @@
         <v>0.41</v>
       </c>
       <c r="C20" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005781072814483268</v>
+        <v>0.02969292014118242</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.004909453284285714</v>
+        <v>0.02193046350231187</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5407659792485753</v>
+        <v>3.825196264864782</v>
       </c>
       <c r="G20" t="n">
-        <v>0.803</v>
+        <v>0.003</v>
       </c>
       <c r="H20" t="n">
-        <v>15.24653596091313</v>
+        <v>96.60005875174375</v>
       </c>
       <c r="I20" t="n">
-        <v>2637.31948207193</v>
+        <v>3253.302750030464</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1621971910735439</v>
+        <v>0.7666671329503475</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1153,28 +1153,28 @@
         <v>0.43</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.005083311992367624</v>
+        <v>0.0295451146801545</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.005068899109750946</v>
+        <v>0.02213706212046118</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5007098395842823</v>
+        <v>3.9882431235581</v>
       </c>
       <c r="G21" t="n">
-        <v>0.848</v>
+        <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>14.03026124453807</v>
+        <v>102.2521474161123</v>
       </c>
       <c r="I21" t="n">
-        <v>2760.062979727373</v>
+        <v>3460.881723528905</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1417198105508896</v>
+        <v>0.774637480425093</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1188,28 +1188,28 @@
         <v>0.45</v>
       </c>
       <c r="C22" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00479901309827974</v>
+        <v>0.02928980837384457</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.004957859322325175</v>
+        <v>0.0222043325225586</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4918597775394623</v>
+        <v>4.133781412652663</v>
       </c>
       <c r="G22" t="n">
-        <v>0.847</v>
+        <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>13.78022798467055</v>
+        <v>105.6825261084009</v>
       </c>
       <c r="I22" t="n">
-        <v>2871.471217615602</v>
+        <v>3608.167208180648</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1337886212103936</v>
+        <v>0.7658154065826157</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1223,28 +1223,28 @@
         <v>0.47</v>
       </c>
       <c r="C23" t="n">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.003613590009249645</v>
+        <v>0.02590125278153877</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.005698432514028351</v>
+        <v>0.01908937343036066</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3880564077477747</v>
+        <v>3.802365169174552</v>
       </c>
       <c r="G23" t="n">
-        <v>0.929</v>
+        <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>10.66091797769133</v>
+        <v>98.78871220907899</v>
       </c>
       <c r="I23" t="n">
-        <v>2950.228982923563</v>
+        <v>3814.051507172313</v>
       </c>
       <c r="J23" t="n">
-        <v>0.09871220349714191</v>
+        <v>0.6860327236741597</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -1258,28 +1258,28 @@
         <v>0.49</v>
       </c>
       <c r="C24" t="n">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.007180532392186778</v>
+        <v>0.02607264226511007</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.001683927140025743</v>
+        <v>0.01953621704541275</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8100361185127409</v>
+        <v>3.988822848694303</v>
       </c>
       <c r="G24" t="n">
-        <v>0.489</v>
+        <v>0.004</v>
       </c>
       <c r="H24" t="n">
-        <v>22.49366803776725</v>
+        <v>102.8910876827643</v>
       </c>
       <c r="I24" t="n">
-        <v>3132.590566995127</v>
+        <v>3946.323760996457</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1990590091837811</v>
+        <v>0.6859405845517621</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1293,28 +1293,28 @@
         <v>0.51</v>
       </c>
       <c r="C25" t="n">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.005783585518961077</v>
+        <v>0.02657783713776926</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.002787245640358149</v>
+        <v>0.02033795147839601</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6747986760505049</v>
+        <v>4.25934681957597</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.003</v>
       </c>
       <c r="H25" t="n">
-        <v>18.79497719120003</v>
+        <v>110.1526078764079</v>
       </c>
       <c r="I25" t="n">
-        <v>3249.710258382456</v>
+        <v>4144.528665196465</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1606408306940175</v>
+        <v>0.701608967365655</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -1328,28 +1328,28 @@
         <v>0.53</v>
       </c>
       <c r="C26" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.008466771903940537</v>
+        <v>0.02815454873628269</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0002722824155433345</v>
+        <v>0.02215550274082756</v>
       </c>
       <c r="F26" t="n">
-        <v>1.033227501960785</v>
+        <v>4.693171007125623</v>
       </c>
       <c r="G26" t="n">
-        <v>0.384</v>
+        <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>28.42641715680328</v>
+        <v>122.2906137594566</v>
       </c>
       <c r="I26" t="n">
-        <v>3357.409114041832</v>
+        <v>4343.547286263587</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2330034193180595</v>
+        <v>0.7502491641684453</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1363,28 +1363,28 @@
         <v>0.55</v>
       </c>
       <c r="C27" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.008818389808069141</v>
+        <v>0.02655499033016014</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0009518690922601936</v>
+        <v>0.02076067479641119</v>
       </c>
       <c r="F27" t="n">
-        <v>1.121002553307619</v>
+        <v>4.582938256553401</v>
       </c>
       <c r="G27" t="n">
-        <v>0.309</v>
+        <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>30.55693763389969</v>
+        <v>118.8500949882243</v>
       </c>
       <c r="I27" t="n">
-        <v>3465.138001264018</v>
+        <v>4475.621851507095</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2406058081409424</v>
+        <v>0.7032549999303219</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -1398,28 +1398,28 @@
         <v>0.57</v>
       </c>
       <c r="C28" t="n">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00729356185579655</v>
+        <v>0.02228318643578999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0003426415145435513</v>
+        <v>0.01666412428886921</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9551293361470258</v>
+        <v>3.965641570275426</v>
       </c>
       <c r="G28" t="n">
-        <v>0.406</v>
+        <v>0.002</v>
       </c>
       <c r="H28" t="n">
-        <v>25.83292848979556</v>
+        <v>102.635153284858</v>
       </c>
       <c r="I28" t="n">
-        <v>3541.881045303655</v>
+        <v>4605.945993433474</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1971979274030195</v>
+        <v>0.5864865901991891</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1433,28 +1433,28 @@
         <v>0.59</v>
       </c>
       <c r="C29" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00918744567847766</v>
+        <v>0.02035535493466172</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00184809342424419</v>
+        <v>0.01491288468429874</v>
       </c>
       <c r="F29" t="n">
-        <v>1.251806066833506</v>
+        <v>3.740094846325361</v>
       </c>
       <c r="G29" t="n">
-        <v>0.224</v>
+        <v>0.003</v>
       </c>
       <c r="H29" t="n">
-        <v>33.82286466517058</v>
+        <v>96.27860406084315</v>
       </c>
       <c r="I29" t="n">
-        <v>3681.422002244149</v>
+        <v>4729.890702956843</v>
       </c>
       <c r="J29" t="n">
-        <v>0.248697534302725</v>
+        <v>0.5319259892864262</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -1468,28 +1468,28 @@
         <v>0.61</v>
       </c>
       <c r="C30" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.009932071789190412</v>
+        <v>0.01854505654354054</v>
       </c>
       <c r="E30" t="n">
-        <v>0.002860158016256054</v>
+        <v>0.01329663438601936</v>
       </c>
       <c r="F30" t="n">
-        <v>1.40443903985403</v>
+        <v>3.533453671779207</v>
       </c>
       <c r="G30" t="n">
-        <v>0.158</v>
+        <v>0.005</v>
       </c>
       <c r="H30" t="n">
-        <v>37.27585600441313</v>
+        <v>91.2591189489228</v>
       </c>
       <c r="I30" t="n">
-        <v>3753.07959865759</v>
+        <v>4920.940453034609</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2643677730809443</v>
+        <v>0.4854208454729935</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1503,28 +1503,28 @@
         <v>0.63</v>
       </c>
       <c r="C31" t="n">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.009516461039454444</v>
+        <v>0.02004294376719795</v>
       </c>
       <c r="E31" t="n">
-        <v>0.002638103130006231</v>
+        <v>0.01496544606650985</v>
       </c>
       <c r="F31" t="n">
-        <v>1.383536763386864</v>
+        <v>3.947405779126551</v>
       </c>
       <c r="G31" t="n">
-        <v>0.183</v>
+        <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>36.42741490066355</v>
+        <v>103.709601846224</v>
       </c>
       <c r="I31" t="n">
-        <v>3827.832084809528</v>
+        <v>5174.369745823165</v>
       </c>
       <c r="J31" t="n">
-        <v>0.251223551039059</v>
+        <v>0.5345855765269281</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1538,28 +1538,28 @@
         <v>0.65</v>
       </c>
       <c r="C32" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.009459882503292273</v>
+        <v>0.01893673822891722</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002811962251636491</v>
+        <v>0.01400677208936407</v>
       </c>
       <c r="F32" t="n">
-        <v>1.422983752089408</v>
+        <v>3.841149754962319</v>
       </c>
       <c r="G32" t="n">
-        <v>0.172</v>
+        <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>37.42776774691912</v>
+        <v>101.1093795680006</v>
       </c>
       <c r="I32" t="n">
-        <v>3956.472792753328</v>
+        <v>5339.3239292711</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2495184516461276</v>
+        <v>0.505546897840003</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -1573,28 +1573,28 @@
         <v>0.67</v>
       </c>
       <c r="C33" t="n">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.009722471075695134</v>
+        <v>0.01511459923305191</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003292097511251479</v>
+        <v>0.01031028020492042</v>
       </c>
       <c r="F33" t="n">
-        <v>1.511960538257855</v>
+        <v>3.14604403757309</v>
       </c>
       <c r="G33" t="n">
-        <v>0.141</v>
+        <v>0.008</v>
       </c>
       <c r="H33" t="n">
-        <v>40.08424505831165</v>
+        <v>81.96816987500146</v>
       </c>
       <c r="I33" t="n">
-        <v>4122.845390460133</v>
+        <v>5423.112357207412</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2586080326342688</v>
+        <v>0.3979037372572887</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -1608,28 +1608,28 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.009161515358119633</v>
+        <v>0.01577830099534013</v>
       </c>
       <c r="E34" t="n">
-        <v>0.002890385708487431</v>
+        <v>0.01111374318015224</v>
       </c>
       <c r="F34" t="n">
-        <v>1.460903516586843</v>
+        <v>3.382593081806262</v>
       </c>
       <c r="G34" t="n">
-        <v>0.148</v>
+        <v>0.002</v>
       </c>
       <c r="H34" t="n">
-        <v>39.15574050879979</v>
+        <v>89.39252951453602</v>
       </c>
       <c r="I34" t="n">
-        <v>4273.937113918277</v>
+        <v>5665.535822959435</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2462625189232691</v>
+        <v>0.4216628750685661</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -1643,28 +1643,28 @@
         <v>0.71</v>
       </c>
       <c r="C35" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.006618537379638296</v>
+        <v>0.01695135963936803</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0005241725782864082</v>
+        <v>0.01244196220652094</v>
       </c>
       <c r="F35" t="n">
-        <v>1.086009386600898</v>
+        <v>3.759118572227079</v>
       </c>
       <c r="G35" t="n">
-        <v>0.302</v>
+        <v>0.004</v>
       </c>
       <c r="H35" t="n">
-        <v>29.41734211713435</v>
+        <v>99.82905568507152</v>
       </c>
       <c r="I35" t="n">
-        <v>4444.689276460959</v>
+        <v>5889.147408165856</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1793740372995998</v>
+        <v>0.4558404369181348</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1678,28 +1678,28 @@
         <v>0.73</v>
       </c>
       <c r="C36" t="n">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.007281561955579515</v>
+        <v>0.01925181798228626</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001372523633886513</v>
+        <v>0.01487347788399285</v>
       </c>
       <c r="F36" t="n">
-        <v>1.23227529746216</v>
+        <v>4.397058599853955</v>
       </c>
       <c r="G36" t="n">
-        <v>0.254</v>
+        <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>33.27931532695398</v>
+        <v>117.7432616062137</v>
       </c>
       <c r="I36" t="n">
-        <v>4570.35393367128</v>
+        <v>6115.955475714043</v>
       </c>
       <c r="J36" t="n">
-        <v>0.196919025603278</v>
+        <v>0.5233033849165052</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1713,28 +1713,28 @@
         <v>0.75</v>
       </c>
       <c r="C37" t="n">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.006022341323910664</v>
+        <v>0.02034885175928614</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0002434014478869262</v>
+        <v>0.01608949894084832</v>
       </c>
       <c r="F37" t="n">
-        <v>1.04211870223754</v>
+        <v>4.777451558180394</v>
       </c>
       <c r="G37" t="n">
-        <v>0.361</v>
+        <v>0.002</v>
       </c>
       <c r="H37" t="n">
-        <v>28.46697078450602</v>
+        <v>128.4643690738876</v>
       </c>
       <c r="I37" t="n">
-        <v>4726.894284700011</v>
+        <v>6313.101623302319</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1645489640722892</v>
+        <v>0.5561228098436687</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1748,28 +1748,28 @@
         <v>0.77</v>
       </c>
       <c r="C38" t="n">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.006701025033198496</v>
+        <v>0.02080666789081371</v>
       </c>
       <c r="E38" t="n">
-        <v>0.001089166417566734</v>
+        <v>0.0166575436022155</v>
       </c>
       <c r="F38" t="n">
-        <v>1.194083011024728</v>
+        <v>5.014713092107226</v>
       </c>
       <c r="G38" t="n">
-        <v>0.283</v>
+        <v>0.002</v>
       </c>
       <c r="H38" t="n">
-        <v>32.7478460332174</v>
+        <v>134.7214271473193</v>
       </c>
       <c r="I38" t="n">
-        <v>4886.990553083545</v>
+        <v>6474.916015110702</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1839766631079629</v>
+        <v>0.5684448402840476</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1783,28 +1783,28 @@
         <v>0.79</v>
       </c>
       <c r="C39" t="n">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00811350863539115</v>
+        <v>0.02103708131142978</v>
       </c>
       <c r="E39" t="n">
-        <v>0.002663582858662528</v>
+        <v>0.01699177999453472</v>
       </c>
       <c r="F39" t="n">
-        <v>1.488737455845018</v>
+        <v>5.200374375963017</v>
       </c>
       <c r="G39" t="n">
-        <v>0.161</v>
+        <v>0.002</v>
       </c>
       <c r="H39" t="n">
-        <v>40.62855775638363</v>
+        <v>139.9905202454202</v>
       </c>
       <c r="I39" t="n">
-        <v>5007.520122572094</v>
+        <v>6654.464950390295</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2220139768108395</v>
+        <v>0.576092675907079</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -1818,28 +1818,28 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>188</v>
+        <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.008449010294435485</v>
+        <v>0.0214102405902621</v>
       </c>
       <c r="E40" t="n">
-        <v>0.003118090994943201</v>
+        <v>0.0174801612352028</v>
       </c>
       <c r="F40" t="n">
-        <v>1.584906808707491</v>
+        <v>5.447788366588759</v>
       </c>
       <c r="G40" t="n">
-        <v>0.148</v>
+        <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>43.20937952879291</v>
+        <v>146.8932762790547</v>
       </c>
       <c r="I40" t="n">
-        <v>5114.135031561104</v>
+        <v>6860.888632230754</v>
       </c>
       <c r="J40" t="n">
-        <v>0.2310662006887322</v>
+        <v>0.5875731051162184</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -1853,28 +1853,28 @@
         <v>0.83</v>
       </c>
       <c r="C41" t="n">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.007329538588903467</v>
+        <v>0.02355520666208049</v>
       </c>
       <c r="E41" t="n">
-        <v>0.002132311042248647</v>
+        <v>0.01972601139408858</v>
       </c>
       <c r="F41" t="n">
-        <v>1.410278561619053</v>
+        <v>6.151477011104118</v>
       </c>
       <c r="G41" t="n">
-        <v>0.196</v>
+        <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>38.66472845696204</v>
+        <v>166.9109081744038</v>
       </c>
       <c r="I41" t="n">
-        <v>5275.192699783092</v>
+        <v>7085.945394955902</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2013787940466772</v>
+        <v>0.6519957350562648</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -1888,28 +1888,28 @@
         <v>0.85</v>
       </c>
       <c r="C42" t="n">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.007152079722855433</v>
+        <v>0.02050417980379317</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0020865291091966</v>
+        <v>0.01675132225514864</v>
       </c>
       <c r="F42" t="n">
-        <v>1.411905687719387</v>
+        <v>5.463617933273079</v>
       </c>
       <c r="G42" t="n">
-        <v>0.18</v>
+        <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>38.42622572844039</v>
+        <v>148.2199230527915</v>
       </c>
       <c r="I42" t="n">
-        <v>5372.734535612657</v>
+        <v>7228.76625503311</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1950569833930983</v>
+        <v>0.5657248971480592</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -1923,28 +1923,28 @@
         <v>0.87</v>
       </c>
       <c r="C43" t="n">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.007981493875672022</v>
+        <v>0.02083349629767358</v>
       </c>
       <c r="E43" t="n">
-        <v>0.003021401345050467</v>
+        <v>0.01716620602163488</v>
       </c>
       <c r="F43" t="n">
-        <v>1.609142133215752</v>
+        <v>5.680896446565842</v>
       </c>
       <c r="G43" t="n">
-        <v>0.124</v>
+        <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>43.67341292795399</v>
+        <v>154.2981166524853</v>
       </c>
       <c r="I43" t="n">
-        <v>5471.834422008724</v>
+        <v>7406.251665483311</v>
       </c>
       <c r="J43" t="n">
-        <v>0.2172806613331044</v>
+        <v>0.5757392412406168</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
@@ -1958,28 +1958,28 @@
         <v>0.89</v>
       </c>
       <c r="C44" t="n">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.008527756639643917</v>
+        <v>0.02016971101590353</v>
       </c>
       <c r="E44" t="n">
-        <v>0.003691306672032435</v>
+        <v>0.01658058907823279</v>
       </c>
       <c r="F44" t="n">
-        <v>1.763226477427077</v>
+        <v>5.619678396603472</v>
       </c>
       <c r="G44" t="n">
-        <v>0.096</v>
+        <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>47.64192668294518</v>
+        <v>151.813517123292</v>
       </c>
       <c r="I44" t="n">
-        <v>5586.689289591935</v>
+        <v>7526.806755118563</v>
       </c>
       <c r="J44" t="n">
-        <v>0.2312714887521613</v>
+        <v>0.554063931106905</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -1993,28 +1993,28 @@
         <v>0.91</v>
       </c>
       <c r="C45" t="n">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.008111891581495939</v>
+        <v>0.02202003047816982</v>
       </c>
       <c r="E45" t="n">
-        <v>0.00338861487474118</v>
+        <v>0.01852724487273472</v>
       </c>
       <c r="F45" t="n">
-        <v>1.717428828570447</v>
+        <v>6.304432325850331</v>
       </c>
       <c r="G45" t="n">
-        <v>0.121</v>
+        <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>45.98818162914067</v>
+        <v>170.0609150495969</v>
       </c>
       <c r="I45" t="n">
-        <v>5669.230310479549</v>
+        <v>7723.009975766909</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2179534674366856</v>
+        <v>0.6051989859416259</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -2028,28 +2028,28 @@
         <v>0.93</v>
       </c>
       <c r="C46" t="n">
-        <v>216</v>
+        <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.007766551488017704</v>
+        <v>0.01877498934257275</v>
       </c>
       <c r="E46" t="n">
-        <v>0.003129946588429022</v>
+        <v>0.01534413266195234</v>
       </c>
       <c r="F46" t="n">
-        <v>1.675051391311485</v>
+        <v>5.472391035342758</v>
       </c>
       <c r="G46" t="n">
-        <v>0.106</v>
+        <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>44.79488593322327</v>
+        <v>147.0567626127062</v>
       </c>
       <c r="I46" t="n">
-        <v>5767.667413566132</v>
+        <v>7832.588340236835</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2083483066661547</v>
+        <v>0.5123929010895686</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -2063,28 +2063,28 @@
         <v>0.95</v>
       </c>
       <c r="C47" t="n">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.009289322132112159</v>
+        <v>0.01790754026609667</v>
       </c>
       <c r="E47" t="n">
-        <v>0.004765529082487174</v>
+        <v>0.01454420992454231</v>
       </c>
       <c r="F47" t="n">
-        <v>2.053436580809565</v>
+        <v>5.324347729048869</v>
       </c>
       <c r="G47" t="n">
-        <v>0.068</v>
+        <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>54.48540707547501</v>
+        <v>143.0602247218348</v>
       </c>
       <c r="I47" t="n">
-        <v>5865.380304459997</v>
+        <v>7988.826080859505</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2476609412521591</v>
+        <v>0.4882601526342485</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -2098,28 +2098,28 @@
         <v>0.97</v>
       </c>
       <c r="C48" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01037797495634475</v>
+        <v>0.01842381388779488</v>
       </c>
       <c r="E48" t="n">
-        <v>0.00596001948739977</v>
+        <v>0.01512993406862639</v>
       </c>
       <c r="F48" t="n">
-        <v>2.349044717470465</v>
+        <v>5.593347328757702</v>
       </c>
       <c r="G48" t="n">
-        <v>0.039</v>
+        <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>61.72923771638558</v>
+        <v>150.1810297583538</v>
       </c>
       <c r="I48" t="n">
-        <v>5948.100470087027</v>
+        <v>8151.462594715167</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2743521676283804</v>
+        <v>0.5022776914995108</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -2133,28 +2133,28 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>230</v>
+        <v>306</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0100692791705544</v>
+        <v>0.0189965839650381</v>
       </c>
       <c r="E49" t="n">
-        <v>0.005727477763407873</v>
+        <v>0.01576959904387043</v>
       </c>
       <c r="F49" t="n">
-        <v>2.319147797497178</v>
+        <v>5.886790434138272</v>
       </c>
       <c r="G49" t="n">
-        <v>0.037</v>
+        <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>60.99952929470849</v>
+        <v>157.4700454452571</v>
       </c>
       <c r="I49" t="n">
-        <v>6057.983720730425</v>
+        <v>8289.387488564778</v>
       </c>
       <c r="J49" t="n">
-        <v>0.266373490369906</v>
+        <v>0.5162952309680561</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>

--- a/results/01_pollution_assessment/SumRel_Focus/tables/SumRel_single_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/SumRel_single_cutoff_metrics.xlsx
@@ -491,25 +491,25 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1343547582722011</v>
+        <v>0.08596937430411158</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06776666275467813</v>
+        <v>0.01565932617365862</v>
       </c>
       <c r="F2" t="n">
-        <v>2.017699368453104</v>
+        <v>1.222718183105271</v>
       </c>
       <c r="G2" t="n">
-        <v>0.095</v>
+        <v>0.284</v>
       </c>
       <c r="H2" t="n">
-        <v>41.79168011798258</v>
+        <v>28.79429621116877</v>
       </c>
       <c r="I2" t="n">
-        <v>311.0547081132261</v>
+        <v>334.9366730216117</v>
       </c>
       <c r="J2" t="n">
-        <v>2.985120008427327</v>
+        <v>2.056735443654912</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -526,25 +526,25 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0481288230804835</v>
+        <v>0.06129173565229126</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.001969659915280531</v>
+        <v>0.01188603752872774</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9606842403701712</v>
+        <v>1.240580297013528</v>
       </c>
       <c r="G3" t="n">
-        <v>0.438</v>
+        <v>0.283</v>
       </c>
       <c r="H3" t="n">
-        <v>20.25237696540423</v>
+        <v>26.82787748697346</v>
       </c>
       <c r="I3" t="n">
-        <v>420.7951840321789</v>
+        <v>437.7079095812906</v>
       </c>
       <c r="J3" t="n">
-        <v>1.012618848270211</v>
+        <v>1.341393874348673</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -561,25 +561,25 @@
         <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06840106269008149</v>
+        <v>0.06484176821503465</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03113710519768476</v>
+        <v>0.02743543894363598</v>
       </c>
       <c r="F4" t="n">
-        <v>1.835582350694714</v>
+        <v>1.733443764144308</v>
       </c>
       <c r="G4" t="n">
-        <v>0.11</v>
+        <v>0.119</v>
       </c>
       <c r="H4" t="n">
-        <v>39.74632712226193</v>
+        <v>32.15556509422809</v>
       </c>
       <c r="I4" t="n">
-        <v>581.0776259770794</v>
+        <v>495.908208233783</v>
       </c>
       <c r="J4" t="n">
-        <v>1.528704889317767</v>
+        <v>1.236752503624158</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -596,25 +596,25 @@
         <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05504500847979561</v>
+        <v>0.02193980389987113</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02551516499478923</v>
+        <v>-0.008624577228257824</v>
       </c>
       <c r="F5" t="n">
-        <v>1.864046739961368</v>
+        <v>0.717822612141146</v>
       </c>
       <c r="G5" t="n">
-        <v>0.108</v>
+        <v>0.68</v>
       </c>
       <c r="H5" t="n">
-        <v>38.6651998044837</v>
+        <v>14.59687501489906</v>
       </c>
       <c r="I5" t="n">
-        <v>702.4288100287212</v>
+        <v>665.3147439929851</v>
       </c>
       <c r="J5" t="n">
-        <v>1.171672721347991</v>
+        <v>0.4423295459060318</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -631,25 +631,25 @@
         <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05389415588297435</v>
+        <v>0.01996068506582924</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02899663366936833</v>
+        <v>-0.005829823221912056</v>
       </c>
       <c r="F6" t="n">
-        <v>2.164639333207317</v>
+        <v>0.773954698493356</v>
       </c>
       <c r="G6" t="n">
-        <v>0.057</v>
+        <v>0.639</v>
       </c>
       <c r="H6" t="n">
-        <v>42.62214316319016</v>
+        <v>16.07295162891083</v>
       </c>
       <c r="I6" t="n">
-        <v>790.8490719427871</v>
+        <v>805.2304605730275</v>
       </c>
       <c r="J6" t="n">
-        <v>1.092875465722825</v>
+        <v>0.4121269648438677</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -666,25 +666,25 @@
         <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04401686981157218</v>
+        <v>0.02752029812662128</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02228998048910791</v>
+        <v>0.005418486720408122</v>
       </c>
       <c r="F7" t="n">
-        <v>2.025916787179536</v>
+        <v>1.24516030024964</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.224</v>
       </c>
       <c r="H7" t="n">
-        <v>41.25617865491397</v>
+        <v>26.93887130497776</v>
       </c>
       <c r="I7" t="n">
-        <v>937.2810659077712</v>
+        <v>978.8728007607924</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9168039701091987</v>
+        <v>0.5986415845550613</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -701,25 +701,25 @@
         <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03304315799902453</v>
+        <v>0.02270754285670047</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01370402115900504</v>
+        <v>0.003161693713834457</v>
       </c>
       <c r="F8" t="n">
-        <v>1.708615967319004</v>
+        <v>1.161757808050435</v>
       </c>
       <c r="G8" t="n">
-        <v>0.125</v>
+        <v>0.318</v>
       </c>
       <c r="H8" t="n">
-        <v>38.31202882667672</v>
+        <v>26.77148116811826</v>
       </c>
       <c r="I8" t="n">
-        <v>1159.454215235957</v>
+        <v>1178.96865094845</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7512162515034653</v>
+        <v>0.5249310032964366</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -736,25 +736,25 @@
         <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0313986395467045</v>
+        <v>0.01518979689771847</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01410218668146712</v>
+        <v>-0.002396099586250866</v>
       </c>
       <c r="F9" t="n">
-        <v>1.815322470528613</v>
+        <v>0.8637487950395337</v>
       </c>
       <c r="G9" t="n">
-        <v>0.095</v>
+        <v>0.538</v>
       </c>
       <c r="H9" t="n">
-        <v>40.86784678954074</v>
+        <v>19.79924189206775</v>
       </c>
       <c r="I9" t="n">
-        <v>1301.580176069447</v>
+        <v>1303.456657477865</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7169797682375573</v>
+        <v>0.3473551209134694</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -771,25 +771,25 @@
         <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02830411144828157</v>
+        <v>0.01255073208506302</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01288036718555596</v>
+        <v>-0.003123065818348758</v>
       </c>
       <c r="F10" t="n">
-        <v>1.835099893135783</v>
+        <v>0.8007460707612616</v>
       </c>
       <c r="G10" t="n">
-        <v>0.092</v>
+        <v>0.612</v>
       </c>
       <c r="H10" t="n">
-        <v>43.34061093145996</v>
+        <v>18.60223603334417</v>
       </c>
       <c r="I10" t="n">
-        <v>1531.247889927713</v>
+        <v>1482.163423397685</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6771970458040619</v>
+        <v>0.2906599380210028</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -806,25 +806,25 @@
         <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02918701822684298</v>
+        <v>0.0176795923241924</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01511726486781162</v>
+        <v>0.003443064676716845</v>
       </c>
       <c r="F11" t="n">
-        <v>2.074451305723001</v>
+        <v>1.241847223000861</v>
       </c>
       <c r="G11" t="n">
-        <v>0.049</v>
+        <v>0.242</v>
       </c>
       <c r="H11" t="n">
-        <v>47.77410718496151</v>
+        <v>29.91639739955398</v>
       </c>
       <c r="I11" t="n">
-        <v>1636.827263876657</v>
+        <v>1692.142943738413</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6824872454994503</v>
+        <v>0.4273771057079138</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -841,25 +841,25 @@
         <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0387055046905635</v>
+        <v>0.01838310744045406</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02588824475310436</v>
+        <v>0.005294882206326679</v>
       </c>
       <c r="F12" t="n">
-        <v>3.019795563125353</v>
+        <v>1.404553108737805</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01</v>
+        <v>0.169</v>
       </c>
       <c r="H12" t="n">
-        <v>68.74811577124862</v>
+        <v>34.07914537955621</v>
       </c>
       <c r="I12" t="n">
-        <v>1776.184455437668</v>
+        <v>1853.829418662989</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9045804706743241</v>
+        <v>0.4484098076257398</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -876,25 +876,25 @@
         <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03641551275115183</v>
+        <v>0.01940516189915653</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02451940797030183</v>
+        <v>0.007299052786800431</v>
       </c>
       <c r="F13" t="n">
-        <v>3.061129119320849</v>
+        <v>1.60292309602188</v>
       </c>
       <c r="G13" t="n">
-        <v>0.011</v>
+        <v>0.109</v>
       </c>
       <c r="H13" t="n">
-        <v>71.54382009164084</v>
+        <v>38.50337799912614</v>
       </c>
       <c r="I13" t="n">
-        <v>1964.652278289776</v>
+        <v>1984.182260329389</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8724856108736692</v>
+        <v>0.4695533902332452</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -911,25 +911,25 @@
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03359390921283926</v>
+        <v>0.01594354209573559</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02248579322677979</v>
+        <v>0.004632548326720887</v>
       </c>
       <c r="F14" t="n">
-        <v>3.024267054377142</v>
+        <v>1.409561566501036</v>
       </c>
       <c r="G14" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.175</v>
       </c>
       <c r="H14" t="n">
-        <v>71.65637540578577</v>
+        <v>34.24480772263615</v>
       </c>
       <c r="I14" t="n">
-        <v>2133.016879690781</v>
+        <v>2147.879531223842</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8142769932475656</v>
+        <v>0.3891455423026833</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -946,25 +946,25 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03821215594670818</v>
+        <v>0.0238295030684046</v>
       </c>
       <c r="E15" t="n">
-        <v>0.027980370371673</v>
+        <v>0.01344471054785568</v>
       </c>
       <c r="F15" t="n">
-        <v>3.734651754229847</v>
+        <v>2.294653746933511</v>
       </c>
       <c r="G15" t="n">
-        <v>0.003</v>
+        <v>0.031</v>
       </c>
       <c r="H15" t="n">
-        <v>86.89963145042185</v>
+        <v>55.98045128132983</v>
       </c>
       <c r="I15" t="n">
-        <v>2274.135789972559</v>
+        <v>2349.207665834794</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9147329626360193</v>
+        <v>0.5892679082245239</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -981,25 +981,25 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.04330395020545587</v>
+        <v>0.01704624068506844</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03373698970751038</v>
+        <v>0.00721670309191913</v>
       </c>
       <c r="F16" t="n">
-        <v>4.52640629327942</v>
+        <v>1.734185410405144</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001</v>
+        <v>0.096</v>
       </c>
       <c r="H16" t="n">
-        <v>105.7681619497189</v>
+        <v>42.33565125919232</v>
       </c>
       <c r="I16" t="n">
-        <v>2442.459901415486</v>
+        <v>2483.576997494585</v>
       </c>
       <c r="J16" t="n">
-        <v>1.047209524254643</v>
+        <v>0.4191648639523989</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1016,25 +1016,25 @@
         <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04507400869751438</v>
+        <v>0.01802024255867515</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03606527293050965</v>
+        <v>0.008756282582813468</v>
       </c>
       <c r="F17" t="n">
-        <v>5.003366716848611</v>
+        <v>1.945198662950749</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>114.3700791458616</v>
+        <v>48.02902230293112</v>
       </c>
       <c r="I17" t="n">
-        <v>2537.384236520515</v>
+        <v>2665.281676789051</v>
       </c>
       <c r="J17" t="n">
-        <v>1.068879244353846</v>
+        <v>0.4488693673171135</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1051,25 +1051,25 @@
         <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03488805987272605</v>
+        <v>0.02079437683938289</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02627098897873259</v>
+        <v>0.01205146948973457</v>
       </c>
       <c r="F18" t="n">
-        <v>4.048714499615477</v>
+        <v>2.378428136976566</v>
       </c>
       <c r="G18" t="n">
-        <v>0.002</v>
+        <v>0.021</v>
       </c>
       <c r="H18" t="n">
-        <v>100.5126740482152</v>
+        <v>58.65382870312249</v>
       </c>
       <c r="I18" t="n">
-        <v>2881.004974621463</v>
+        <v>2820.658159471113</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8894926906921699</v>
+        <v>0.5190604310010839</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1086,25 +1086,25 @@
         <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03392185882007112</v>
+        <v>0.03111366345822435</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02573475592871588</v>
+        <v>0.02290276230109067</v>
       </c>
       <c r="F19" t="n">
-        <v>4.143328753799935</v>
+        <v>3.789311655663103</v>
       </c>
       <c r="G19" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H19" t="n">
-        <v>104.4307817734263</v>
+        <v>96.32747530169513</v>
       </c>
       <c r="I19" t="n">
-        <v>3078.568964258409</v>
+        <v>3095.9862836799</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8775695947346751</v>
+        <v>0.8094745823671859</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1121,25 +1121,25 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02969292014118242</v>
+        <v>0.03439470916883483</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02193046350231187</v>
+        <v>0.02666986684218542</v>
       </c>
       <c r="F20" t="n">
-        <v>3.825196264864782</v>
+        <v>4.452480415060285</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H20" t="n">
-        <v>96.60005875174375</v>
+        <v>113.6266442413812</v>
       </c>
       <c r="I20" t="n">
-        <v>3253.302750030464</v>
+        <v>3303.608228917335</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7666671329503475</v>
+        <v>0.9017987638204862</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1156,25 +1156,25 @@
         <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0295451146801545</v>
+        <v>0.04136739047614153</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02213706212046118</v>
+        <v>0.03404958429657023</v>
       </c>
       <c r="F21" t="n">
-        <v>3.9882431235581</v>
+        <v>5.652977061844537</v>
       </c>
       <c r="G21" t="n">
         <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>102.2521474161123</v>
+        <v>144.6813991173338</v>
       </c>
       <c r="I21" t="n">
-        <v>3460.881723528905</v>
+        <v>3497.474640097934</v>
       </c>
       <c r="J21" t="n">
-        <v>0.774637480425093</v>
+        <v>1.096071205434347</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1191,25 +1191,25 @@
         <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02928980837384457</v>
+        <v>0.04939522648582759</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0222043325225586</v>
+        <v>0.04245650551127156</v>
       </c>
       <c r="F22" t="n">
-        <v>4.133781412652663</v>
+        <v>7.118779767475563</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>105.6825261084009</v>
+        <v>183.5487358603085</v>
       </c>
       <c r="I22" t="n">
-        <v>3608.167208180648</v>
+        <v>3715.920523473498</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7658154065826157</v>
+        <v>1.330063303335569</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1226,25 +1226,25 @@
         <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02590125278153877</v>
+        <v>0.04455602613005746</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01908937343036066</v>
+        <v>0.03787459973935847</v>
       </c>
       <c r="F23" t="n">
-        <v>3.802365169174552</v>
+        <v>6.668639826981129</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>98.78871220907899</v>
+        <v>172.6808843934515</v>
       </c>
       <c r="I23" t="n">
-        <v>3814.051507172313</v>
+        <v>3875.589889668396</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6860327236741597</v>
+        <v>1.199172808287858</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -1261,25 +1261,25 @@
         <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02607264226511007</v>
+        <v>0.04480565971403618</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01953621704541275</v>
+        <v>0.03839495944366045</v>
       </c>
       <c r="F24" t="n">
-        <v>3.988822848694303</v>
+        <v>6.989198968026479</v>
       </c>
       <c r="G24" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>102.8910876827643</v>
+        <v>180.9058033482051</v>
       </c>
       <c r="I24" t="n">
-        <v>3946.323760996457</v>
+        <v>4037.565890175546</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6859405845517621</v>
+        <v>1.206038688988034</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1296,25 +1296,25 @@
         <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02657783713776926</v>
+        <v>0.04598058569801633</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02033795147839601</v>
+        <v>0.03986507663197802</v>
       </c>
       <c r="F25" t="n">
-        <v>4.25934681957597</v>
+        <v>7.518684904477245</v>
       </c>
       <c r="G25" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>110.1526078764079</v>
+        <v>199.0911511717016</v>
       </c>
       <c r="I25" t="n">
-        <v>4144.528665196465</v>
+        <v>4329.895936499363</v>
       </c>
       <c r="J25" t="n">
-        <v>0.701608967365655</v>
+        <v>1.268096504278355</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -1331,25 +1331,25 @@
         <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02815454873628269</v>
+        <v>0.04224297482586859</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02215550274082756</v>
+        <v>0.03633089442355908</v>
       </c>
       <c r="F26" t="n">
-        <v>4.693171007125623</v>
+        <v>7.145196267859805</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>122.2906137594566</v>
+        <v>190.5453105648115</v>
       </c>
       <c r="I26" t="n">
-        <v>4343.547286263587</v>
+        <v>4510.698201304849</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7502491641684453</v>
+        <v>1.168989635366941</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1366,25 +1366,25 @@
         <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.02655499033016014</v>
+        <v>0.0335580676464196</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02076067479641119</v>
+        <v>0.02780543709669592</v>
       </c>
       <c r="F27" t="n">
-        <v>4.582938256553401</v>
+        <v>5.833516920016954</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>118.8500949882243</v>
+        <v>155.2716823033675</v>
       </c>
       <c r="I27" t="n">
-        <v>4475.621851507095</v>
+        <v>4626.955399797399</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7032549999303219</v>
+        <v>0.9187673509075001</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -1401,25 +1401,25 @@
         <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02228318643578999</v>
+        <v>0.03392320435846917</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01666412428886921</v>
+        <v>0.02837103886627645</v>
       </c>
       <c r="F28" t="n">
-        <v>3.965641570275426</v>
+        <v>6.109905118313026</v>
       </c>
       <c r="G28" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>102.635153284858</v>
+        <v>163.0895859990352</v>
       </c>
       <c r="I28" t="n">
-        <v>4605.945993433474</v>
+        <v>4807.611458978187</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5864865901991891</v>
+        <v>0.931940491423059</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1436,25 +1436,25 @@
         <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02035535493466172</v>
+        <v>0.02624710205251832</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01491288468429874</v>
+        <v>0.02083736373058787</v>
       </c>
       <c r="F29" t="n">
-        <v>3.740094846325361</v>
+        <v>4.851824707697155</v>
       </c>
       <c r="G29" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>96.27860406084315</v>
+        <v>130.4155942047442</v>
       </c>
       <c r="I29" t="n">
-        <v>4729.890702956843</v>
+        <v>4968.761653907283</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5319259892864262</v>
+        <v>0.7205281447775921</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -1471,25 +1471,25 @@
         <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01854505654354054</v>
+        <v>0.02575062247599957</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01329663438601936</v>
+        <v>0.02054073275661983</v>
       </c>
       <c r="F30" t="n">
-        <v>3.533453671779207</v>
+        <v>4.942642524699272</v>
       </c>
       <c r="G30" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H30" t="n">
-        <v>91.2591189489228</v>
+        <v>133.1361835472564</v>
       </c>
       <c r="I30" t="n">
-        <v>4920.940453034609</v>
+        <v>5170.212241329067</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4854208454729935</v>
+        <v>0.7081711890811506</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1506,25 +1506,25 @@
         <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02004294376719795</v>
+        <v>0.02248706412463384</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01496544606650985</v>
+        <v>0.01742223025999468</v>
       </c>
       <c r="F31" t="n">
-        <v>3.947405779126551</v>
+        <v>4.439842396732932</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>103.709601846224</v>
+        <v>118.3967906263729</v>
       </c>
       <c r="I31" t="n">
-        <v>5174.369745823165</v>
+        <v>5265.106639540067</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5345855765269281</v>
+        <v>0.6102927351874894</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1541,25 +1541,25 @@
         <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01893673822891722</v>
+        <v>0.02194309796600592</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01400677208936407</v>
+        <v>0.01702823916181506</v>
       </c>
       <c r="F32" t="n">
-        <v>3.841149754962319</v>
+        <v>4.464644629728718</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>101.1093795680006</v>
+        <v>118.8825647661189</v>
       </c>
       <c r="I32" t="n">
-        <v>5339.3239292711</v>
+        <v>5417.765757154749</v>
       </c>
       <c r="J32" t="n">
-        <v>0.505546897840003</v>
+        <v>0.594412823830595</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -1576,25 +1576,25 @@
         <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01511459923305191</v>
+        <v>0.01931350178025323</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01031028020492042</v>
+        <v>0.01452966520357157</v>
       </c>
       <c r="F33" t="n">
-        <v>3.14604403757309</v>
+        <v>4.037241128677946</v>
       </c>
       <c r="G33" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="H33" t="n">
-        <v>81.96816987500146</v>
+        <v>107.3984489372119</v>
       </c>
       <c r="I33" t="n">
-        <v>5423.112357207412</v>
+        <v>5560.79628433926</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3979037372572887</v>
+        <v>0.5213516938699603</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -1611,25 +1611,25 @@
         <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01577830099534013</v>
+        <v>0.01964128867088898</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01111374318015224</v>
+        <v>0.01499503885416342</v>
       </c>
       <c r="F34" t="n">
-        <v>3.382593081806262</v>
+        <v>4.227342361184272</v>
       </c>
       <c r="G34" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H34" t="n">
-        <v>89.39252951453602</v>
+        <v>112.3742110552735</v>
       </c>
       <c r="I34" t="n">
-        <v>5665.535822959435</v>
+        <v>5721.325771349572</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4216628750685661</v>
+        <v>0.5300670332795917</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -1646,25 +1646,25 @@
         <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.01695135963936803</v>
+        <v>0.02127099441810731</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01244196220652094</v>
+        <v>0.01678141182369486</v>
       </c>
       <c r="F35" t="n">
-        <v>3.759118572227079</v>
+        <v>4.737855684976322</v>
       </c>
       <c r="G35" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H35" t="n">
-        <v>99.82905568507152</v>
+        <v>126.7685553691596</v>
       </c>
       <c r="I35" t="n">
-        <v>5889.147408165856</v>
+        <v>5959.691064619228</v>
       </c>
       <c r="J35" t="n">
-        <v>0.4558404369181348</v>
+        <v>0.5788518510007293</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1681,25 +1681,25 @@
         <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01925181798228626</v>
+        <v>0.0234904477318062</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01487347788399285</v>
+        <v>0.01913103008775163</v>
       </c>
       <c r="F36" t="n">
-        <v>4.397058599853955</v>
+        <v>5.388437091785296</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>117.7432616062137</v>
+        <v>144.2310792837177</v>
       </c>
       <c r="I36" t="n">
-        <v>6115.955475714043</v>
+        <v>6139.988514924218</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5233033849165052</v>
+        <v>0.6410270190387455</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1716,25 +1716,25 @@
         <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.02034885175928614</v>
+        <v>0.02270176417570689</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01608949894084832</v>
+        <v>0.01845264141125347</v>
       </c>
       <c r="F37" t="n">
-        <v>4.777451558180394</v>
+        <v>5.342694347553629</v>
       </c>
       <c r="G37" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>128.4643690738876</v>
+        <v>142.0490115390862</v>
       </c>
       <c r="I37" t="n">
-        <v>6313.101623302319</v>
+        <v>6257.179417408121</v>
       </c>
       <c r="J37" t="n">
-        <v>0.5561228098436687</v>
+        <v>0.6149307858834901</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1751,25 +1751,25 @@
         <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.02080666789081371</v>
+        <v>0.02524018587715311</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0166575436022155</v>
+        <v>0.02110984768171742</v>
       </c>
       <c r="F38" t="n">
-        <v>5.014713092107226</v>
+        <v>6.110924743413176</v>
       </c>
       <c r="G38" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>134.7214271473193</v>
+        <v>164.5698173423713</v>
       </c>
       <c r="I38" t="n">
-        <v>6474.916015110702</v>
+        <v>6520.150768435367</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5684448402840476</v>
+        <v>0.6943874149467145</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1786,25 +1786,25 @@
         <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.02103708131142978</v>
+        <v>0.02309626906383321</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01699177999453472</v>
+        <v>0.01905947678723741</v>
       </c>
       <c r="F39" t="n">
-        <v>5.200374375963017</v>
+        <v>5.721441055498287</v>
       </c>
       <c r="G39" t="n">
         <v>0.002</v>
       </c>
       <c r="H39" t="n">
-        <v>139.9905202454202</v>
+        <v>153.9553185239491</v>
       </c>
       <c r="I39" t="n">
-        <v>6654.464950390295</v>
+        <v>6665.809014367174</v>
       </c>
       <c r="J39" t="n">
-        <v>0.576092675907079</v>
+        <v>0.6335609815800373</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -1821,25 +1821,25 @@
         <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0214102405902621</v>
+        <v>0.02220314102703188</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0174801612352028</v>
+        <v>0.01827624601107614</v>
       </c>
       <c r="F40" t="n">
-        <v>5.447788366588759</v>
+        <v>5.654121369890572</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>146.8932762790547</v>
+        <v>153.0557320927844</v>
       </c>
       <c r="I40" t="n">
-        <v>6860.888632230754</v>
+        <v>6893.427011360338</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5875731051162184</v>
+        <v>0.6122229283711376</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -1856,25 +1856,25 @@
         <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.02355520666208049</v>
+        <v>0.02286849789866476</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01972601139408858</v>
+        <v>0.0190366096551301</v>
       </c>
       <c r="F41" t="n">
-        <v>6.151477011104118</v>
+        <v>5.967944899554318</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>166.9109081744038</v>
+        <v>161.4965819154298</v>
       </c>
       <c r="I41" t="n">
-        <v>7085.945394955902</v>
+        <v>7061.967193081765</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6519957350562648</v>
+        <v>0.6308460231071477</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -1891,25 +1891,25 @@
         <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.02050417980379317</v>
+        <v>0.02255599078361654</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01675132225514864</v>
+        <v>0.01881099457972235</v>
       </c>
       <c r="F42" t="n">
-        <v>5.463617933273079</v>
+        <v>6.022967596111839</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>148.2199230527915</v>
+        <v>163.28002634593</v>
       </c>
       <c r="I42" t="n">
-        <v>7228.76625503311</v>
+        <v>7238.876266279016</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5657248971480592</v>
+        <v>0.6232062074272144</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -1926,25 +1926,25 @@
         <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.02083349629767358</v>
+        <v>0.02063618605524345</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01716620602163488</v>
+        <v>0.01696815678953267</v>
       </c>
       <c r="F43" t="n">
-        <v>5.680896446565842</v>
+        <v>5.625960034766814</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>154.2981166524853</v>
+        <v>152.5626637877032</v>
       </c>
       <c r="I43" t="n">
-        <v>7406.251665483311</v>
+        <v>7392.968030976757</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5757392412406168</v>
+        <v>0.5692636708496387</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
@@ -1961,25 +1961,25 @@
         <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.02016971101590353</v>
+        <v>0.02256906964731416</v>
       </c>
       <c r="E44" t="n">
-        <v>0.01658058907823279</v>
+        <v>0.01898873656909927</v>
       </c>
       <c r="F44" t="n">
-        <v>5.619678396603472</v>
+        <v>6.303622918392369</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>151.813517123292</v>
+        <v>171.2184496652387</v>
       </c>
       <c r="I44" t="n">
-        <v>7526.806755118563</v>
+        <v>7586.4203682678</v>
       </c>
       <c r="J44" t="n">
-        <v>0.554063931106905</v>
+        <v>0.6248848527928423</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -1996,25 +1996,25 @@
         <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.02202003047816982</v>
+        <v>0.02024890469469263</v>
       </c>
       <c r="E45" t="n">
-        <v>0.01852724487273472</v>
+        <v>0.01674979364003082</v>
       </c>
       <c r="F45" t="n">
-        <v>6.304432325850331</v>
+        <v>5.786871116226886</v>
       </c>
       <c r="G45" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H45" t="n">
-        <v>170.0609150495969</v>
+        <v>157.7983276500266</v>
       </c>
       <c r="I45" t="n">
-        <v>7723.009975766909</v>
+        <v>7792.931520458314</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6051989859416259</v>
+        <v>0.5615598848755393</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -2031,25 +2031,25 @@
         <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01877498934257275</v>
+        <v>0.01838614145922139</v>
       </c>
       <c r="E46" t="n">
-        <v>0.01534413266195234</v>
+        <v>0.01495392517061722</v>
       </c>
       <c r="F46" t="n">
-        <v>5.472391035342758</v>
+        <v>5.356929725049179</v>
       </c>
       <c r="G46" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H46" t="n">
-        <v>147.0567626127062</v>
+        <v>145.3749795670133</v>
       </c>
       <c r="I46" t="n">
-        <v>7832.588340236835</v>
+        <v>7906.76933980087</v>
       </c>
       <c r="J46" t="n">
-        <v>0.5123929010895686</v>
+        <v>0.5065330298502203</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -2066,25 +2066,25 @@
         <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01790754026609667</v>
+        <v>0.01652802745946786</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01454420992454231</v>
+        <v>0.01315997275898673</v>
       </c>
       <c r="F47" t="n">
-        <v>5.324347729048869</v>
+        <v>4.907291872993068</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>143.0602247218348</v>
+        <v>133.2721106531938</v>
       </c>
       <c r="I47" t="n">
-        <v>7988.826080859505</v>
+        <v>8063.40084925565</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4882601526342485</v>
+        <v>0.4548536199767708</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -2101,25 +2101,25 @@
         <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01842381388779488</v>
+        <v>0.01666641717324418</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01512993406862639</v>
+        <v>0.01336664004966437</v>
       </c>
       <c r="F48" t="n">
-        <v>5.593347328757702</v>
+        <v>5.05077056694176</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H48" t="n">
-        <v>150.1810297583538</v>
+        <v>136.2948257098637</v>
       </c>
       <c r="I48" t="n">
-        <v>8151.462594715167</v>
+        <v>8177.8119612095</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5022776914995108</v>
+        <v>0.455835537491183</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -2136,25 +2136,25 @@
         <v>306</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0189965839650381</v>
+        <v>0.01571749956770041</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01576959904387043</v>
+        <v>0.01247972818469933</v>
       </c>
       <c r="F49" t="n">
-        <v>5.886790434138272</v>
+        <v>4.854419200262487</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>157.4700454452571</v>
+        <v>131.0842293431861</v>
       </c>
       <c r="I49" t="n">
-        <v>8289.387488564778</v>
+        <v>8340.018002135988</v>
       </c>
       <c r="J49" t="n">
-        <v>0.5162952309680561</v>
+        <v>0.4297843585022493</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>
